--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2461-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2461-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CE9A5DE-2A83-4A7B-921B-75B3969AF5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE1D5655-B089-40A1-958E-48538382B830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{D1B0DB1F-D713-4C8E-AE25-883EB0532591}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D96AFB58-ADEC-4905-90EC-021B438BC8DB}"/>
   </bookViews>
   <sheets>
     <sheet name="2461-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1526,28 +1526,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1C3617-CCD7-45F5-84ED-E22E9B19FD71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C37752C-03A1-4A80-A2EB-B3ECB2015EF8}">
   <dimension ref="A1:X70"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1617,7 +1617,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1737,7 +1737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>6.03</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2023</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2022</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>8.06</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2021</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>29</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2020</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>29</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>29</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>29</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>29</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2019</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>29</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>29</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>29</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2018</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>2017</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2016</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>2015</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>2014</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35">
         <v>2013</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37">
         <v>2012</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="35">
         <v>2011</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>2010</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="35">
         <v>2009</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="37">
         <v>2008</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="35">
         <v>2007</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="37">
         <v>2006</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="35">
         <v>2005</v>
       </c>
@@ -5469,7 +5469,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="37">
         <v>2004</v>
       </c>
@@ -5541,7 +5541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="35">
         <v>2003</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="37">
         <v>2002</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="35">
         <v>2001</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="37">
         <v>2000</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="35">
         <v>1999</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="37">
         <v>1998</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="35">
         <v>1997</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="37">
         <v>1996</v>
       </c>
@@ -6117,7 +6117,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="35">
         <v>1995</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="37">
         <v>1994</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="35">
         <v>1993</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="37">
         <v>1992</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="35">
         <v>1990</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="37" t="s">
         <v>63</v>
       </c>
